--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751186</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129751190</v>
       </c>
       <c r="B3" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>129751192</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129751194</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129751193</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129751172</v>
       </c>
       <c r="B7" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>129751181</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>129751202</v>
       </c>
       <c r="B9" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129751167</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>129751165</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129751166</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129751182</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>129751206</v>
       </c>
       <c r="B14" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129751163</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129751170</v>
       </c>
       <c r="B16" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>129751191</v>
       </c>
       <c r="B17" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751164</v>
+        <v>129751195</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,46 +2758,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474821</v>
+        <v>474864</v>
       </c>
       <c r="R18" t="n">
-        <v>6991298</v>
+        <v>6991382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,7 +2825,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en hyfsat grov gran.</t>
+          <t>Enstaka bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2843,12 +2834,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2863,12 +2855,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2886,10 +2878,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751195</v>
+        <v>129751164</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2897,37 +2889,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474864</v>
+        <v>474821</v>
       </c>
       <c r="R19" t="n">
-        <v>6991382</v>
+        <v>6991298</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2964,7 +2965,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran i barrblandskog.</t>
+          <t>Ringhack, färska, på en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2973,13 +2974,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
         <v>129751168</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>129751173</v>
       </c>
       <c r="B21" t="n">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129751185</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3399,52 +3399,65 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751188</v>
+        <v>129751183</v>
       </c>
       <c r="B23" t="n">
-        <v>91583</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474794</v>
+        <v>474920</v>
       </c>
       <c r="R23" t="n">
-        <v>6991300</v>
+        <v>6991440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3481,7 +3494,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
+          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3496,27 +3509,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3534,65 +3527,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751183</v>
+        <v>129751188</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>91584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474920</v>
+        <v>474794</v>
       </c>
       <c r="R24" t="n">
-        <v>6991440</v>
+        <v>6991300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3629,7 +3609,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3644,7 +3624,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3662,65 +3662,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751187</v>
+        <v>129751171</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>80209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474778</v>
+        <v>474852</v>
       </c>
       <c r="R25" t="n">
-        <v>6991301</v>
+        <v>6991438</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3757,7 +3740,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>På sidan av ett stort block i tallskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3772,7 +3755,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3790,48 +3773,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751171</v>
+        <v>129751187</v>
       </c>
       <c r="B26" t="n">
-        <v>80208</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474852</v>
+        <v>474778</v>
       </c>
       <c r="R26" t="n">
-        <v>6991438</v>
+        <v>6991301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
         <v>129751203</v>
       </c>
       <c r="B27" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129751180</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4140,65 +4140,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751184</v>
+        <v>129751197</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474889</v>
+        <v>474867</v>
       </c>
       <c r="R29" t="n">
-        <v>6991473</v>
+        <v>6991490</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4235,7 +4218,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4251,6 +4234,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4268,53 +4271,65 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B30" t="n">
-        <v>98667</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R30" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4351,7 +4366,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4366,7 +4381,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4384,37 +4399,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751197</v>
+        <v>129751189</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>98668</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>219795</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4422,10 +4442,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474867</v>
+        <v>474683</v>
       </c>
       <c r="R31" t="n">
-        <v>6991490</v>
+        <v>6991447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4477,27 +4497,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4518,7 +4518,7 @@
         <v>129751205</v>
       </c>
       <c r="B32" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>129751169</v>
       </c>
       <c r="B33" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>129751196</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -2747,10 +2747,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751195</v>
+        <v>129751164</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,37 +2758,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474864</v>
+        <v>474821</v>
       </c>
       <c r="R18" t="n">
-        <v>6991382</v>
+        <v>6991298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,7 +2834,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran i barrblandskog.</t>
+          <t>Ringhack, färska, på en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2834,13 +2843,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2855,12 +2863,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2878,10 +2886,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751164</v>
+        <v>129751195</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,46 +2897,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474821</v>
+        <v>474864</v>
       </c>
       <c r="R19" t="n">
-        <v>6991298</v>
+        <v>6991382</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2965,7 +2964,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en hyfsat grov gran.</t>
+          <t>Enstaka bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2974,12 +2973,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3399,65 +3399,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751183</v>
+        <v>129751188</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>91584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474920</v>
+        <v>474794</v>
       </c>
       <c r="R23" t="n">
-        <v>6991440</v>
+        <v>6991300</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3494,7 +3481,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3509,7 +3496,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3527,52 +3534,65 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751188</v>
+        <v>129751183</v>
       </c>
       <c r="B24" t="n">
-        <v>91584</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474794</v>
+        <v>474920</v>
       </c>
       <c r="R24" t="n">
-        <v>6991300</v>
+        <v>6991440</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3609,7 +3629,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
+          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3624,27 +3644,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4140,48 +4140,65 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751197</v>
+        <v>129751184</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474867</v>
+        <v>474889</v>
       </c>
       <c r="R29" t="n">
-        <v>6991490</v>
+        <v>6991473</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4218,7 +4235,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4234,26 +4251,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4271,65 +4268,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751184</v>
+        <v>129751189</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>98668</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474889</v>
+        <v>474683</v>
       </c>
       <c r="R30" t="n">
-        <v>6991473</v>
+        <v>6991447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4366,7 +4351,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4381,7 +4366,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4399,42 +4384,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751189</v>
+        <v>129751197</v>
       </c>
       <c r="B31" t="n">
-        <v>98668</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4442,10 +4422,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474683</v>
+        <v>474867</v>
       </c>
       <c r="R31" t="n">
-        <v>6991447</v>
+        <v>6991490</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4462,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4497,7 +4477,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129751169</v>
+        <v>129751196</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4637,46 +4637,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474788</v>
+        <v>474884</v>
       </c>
       <c r="R33" t="n">
-        <v>6991283</v>
+        <v>6991431</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4713,7 +4704,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4722,12 +4713,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4742,12 +4734,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4765,10 +4757,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129751196</v>
+        <v>129751169</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4776,37 +4768,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474884</v>
+        <v>474788</v>
       </c>
       <c r="R34" t="n">
-        <v>6991431</v>
+        <v>6991283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4843,7 +4844,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4852,13 +4853,12 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751186</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129751190</v>
       </c>
       <c r="B3" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>129751192</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129751194</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129751193</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,42 +1327,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751172</v>
+        <v>129751167</v>
       </c>
       <c r="B7" t="n">
-        <v>99103</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474858</v>
+        <v>474740</v>
       </c>
       <c r="R7" t="n">
-        <v>6991515</v>
+        <v>6991364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,19 +1412,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en döende gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,65 +1466,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751181</v>
+        <v>129751202</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474845</v>
+        <v>474679</v>
       </c>
       <c r="R8" t="n">
-        <v>6991430</v>
+        <v>6991397</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1535,11 +1547,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1552,7 +1559,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1570,53 +1577,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751202</v>
+        <v>129751181</v>
       </c>
       <c r="B9" t="n">
-        <v>100958</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474679</v>
+        <v>474845</v>
       </c>
       <c r="R9" t="n">
-        <v>6991397</v>
+        <v>6991430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1651,6 +1670,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1663,7 +1687,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1681,42 +1705,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751167</v>
+        <v>129751172</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>99108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1728,10 +1752,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474740</v>
+        <v>474858</v>
       </c>
       <c r="R10" t="n">
-        <v>6991364</v>
+        <v>6991515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,43 +1790,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en döende gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2101,7 +2101,7 @@
         <v>129751182</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>129751206</v>
       </c>
       <c r="B14" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751170</v>
+        <v>129751191</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,29 +2492,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474880</v>
+        <v>474691</v>
       </c>
       <c r="R16" t="n">
-        <v>6991500</v>
+        <v>6991403</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2573,12 +2568,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2616,10 +2612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751191</v>
+        <v>129751170</v>
       </c>
       <c r="B17" t="n">
-        <v>91608</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2627,24 +2623,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2654,10 +2655,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474691</v>
+        <v>474880</v>
       </c>
       <c r="R17" t="n">
-        <v>6991403</v>
+        <v>6991500</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2694,7 +2695,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2703,13 +2704,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751164</v>
+        <v>129751195</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,46 +2758,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474821</v>
+        <v>474864</v>
       </c>
       <c r="R18" t="n">
-        <v>6991298</v>
+        <v>6991382</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,7 +2825,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en hyfsat grov gran.</t>
+          <t>Enstaka bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2843,12 +2834,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2863,12 +2855,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2886,10 +2878,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751195</v>
+        <v>129751164</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2897,37 +2889,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474864</v>
+        <v>474821</v>
       </c>
       <c r="R19" t="n">
-        <v>6991382</v>
+        <v>6991298</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2964,7 +2965,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran i barrblandskog.</t>
+          <t>Ringhack, färska, på en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2973,13 +2974,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
         <v>129751173</v>
       </c>
       <c r="B21" t="n">
-        <v>99103</v>
+        <v>99108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129751185</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3399,52 +3399,65 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751188</v>
+        <v>129751183</v>
       </c>
       <c r="B23" t="n">
-        <v>91584</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474794</v>
+        <v>474920</v>
       </c>
       <c r="R23" t="n">
-        <v>6991300</v>
+        <v>6991440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3481,7 +3494,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
+          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3496,27 +3509,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3534,65 +3527,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751183</v>
+        <v>129751188</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>91589</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474920</v>
+        <v>474794</v>
       </c>
       <c r="R24" t="n">
-        <v>6991440</v>
+        <v>6991300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3629,7 +3609,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3644,7 +3624,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3665,7 +3665,7 @@
         <v>129751171</v>
       </c>
       <c r="B25" t="n">
-        <v>80209</v>
+        <v>80214</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>129751187</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>129751203</v>
       </c>
       <c r="B27" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129751180</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4140,65 +4140,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751184</v>
+        <v>129751197</v>
       </c>
       <c r="B29" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474889</v>
+        <v>474867</v>
       </c>
       <c r="R29" t="n">
-        <v>6991473</v>
+        <v>6991490</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4235,7 +4218,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4251,6 +4234,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4268,53 +4271,65 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B30" t="n">
-        <v>98668</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R30" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4351,7 +4366,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4366,7 +4381,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4384,37 +4399,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751197</v>
+        <v>129751189</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>98673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>219795</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4422,10 +4442,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474867</v>
+        <v>474683</v>
       </c>
       <c r="R31" t="n">
-        <v>6991490</v>
+        <v>6991447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4477,27 +4497,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4518,7 +4518,7 @@
         <v>129751205</v>
       </c>
       <c r="B32" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>129751196</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751202</v>
+        <v>129751172</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>99108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,42 +1477,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474679</v>
+        <v>474858</v>
       </c>
       <c r="R8" t="n">
-        <v>6991397</v>
+        <v>6991515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1705,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751172</v>
+        <v>129751202</v>
       </c>
       <c r="B10" t="n">
-        <v>99108</v>
+        <v>100963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,46 +1720,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474858</v>
+        <v>474679</v>
       </c>
       <c r="R10" t="n">
-        <v>6991515</v>
+        <v>6991397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -4271,65 +4271,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751184</v>
+        <v>129751189</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>98673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474889</v>
+        <v>474683</v>
       </c>
       <c r="R30" t="n">
-        <v>6991473</v>
+        <v>6991447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4366,7 +4354,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4381,7 +4369,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4399,53 +4387,65 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B31" t="n">
-        <v>98673</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R31" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751190</v>
+        <v>129751192</v>
       </c>
       <c r="B3" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,26 +814,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474901</v>
+        <v>474859</v>
       </c>
       <c r="R3" t="n">
-        <v>6991331</v>
+        <v>6991352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en grov gran med 53 cm i brösthöjdsdiameter.</t>
+          <t>På en ung björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +896,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751192</v>
+        <v>129751190</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,26 +945,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474859</v>
+        <v>474901</v>
       </c>
       <c r="R4" t="n">
-        <v>6991352</v>
+        <v>6991331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en ung björk.</t>
+          <t>Flera fruktkroppar i stambasen av en grov gran med 53 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1327,42 +1327,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751167</v>
+        <v>129751172</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>99108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474740</v>
+        <v>474858</v>
       </c>
       <c r="R7" t="n">
-        <v>6991364</v>
+        <v>6991515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,43 +1412,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en döende gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751172</v>
+        <v>129751202</v>
       </c>
       <c r="B8" t="n">
-        <v>99108</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,46 +1453,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474858</v>
+        <v>474679</v>
       </c>
       <c r="R8" t="n">
-        <v>6991515</v>
+        <v>6991397</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1581,50 +1553,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751181</v>
+        <v>129751167</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1636,10 +1600,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474845</v>
+        <v>474740</v>
       </c>
       <c r="R9" t="n">
-        <v>6991430</v>
+        <v>6991364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1676,7 +1640,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+          <t>Ringhack, äldre, på en döende gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,13 +1649,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,53 +1692,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751202</v>
+        <v>129751181</v>
       </c>
       <c r="B10" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474679</v>
+        <v>474845</v>
       </c>
       <c r="R10" t="n">
-        <v>6991397</v>
+        <v>6991430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1790,6 +1785,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -3399,65 +3399,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751183</v>
+        <v>129751188</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>91589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474920</v>
+        <v>474794</v>
       </c>
       <c r="R23" t="n">
-        <v>6991440</v>
+        <v>6991300</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3494,7 +3481,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3509,7 +3496,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3527,52 +3534,65 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751188</v>
+        <v>129751183</v>
       </c>
       <c r="B24" t="n">
-        <v>91589</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474794</v>
+        <v>474920</v>
       </c>
       <c r="R24" t="n">
-        <v>6991300</v>
+        <v>6991440</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3609,7 +3629,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
+          <t>Minst 110 plantor inom ca 2 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3624,27 +3644,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4140,37 +4140,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751197</v>
+        <v>129751189</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>98673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>219795</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4178,10 +4183,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474867</v>
+        <v>474683</v>
       </c>
       <c r="R29" t="n">
-        <v>6991490</v>
+        <v>6991447</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4233,27 +4238,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4271,53 +4256,65 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B30" t="n">
-        <v>98673</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R30" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4354,7 +4351,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4369,7 +4366,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4387,65 +4384,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751184</v>
+        <v>129751197</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474889</v>
+        <v>474867</v>
       </c>
       <c r="R31" t="n">
-        <v>6991473</v>
+        <v>6991490</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4462,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4498,6 +4478,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751192</v>
+        <v>129751190</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,26 +814,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474859</v>
+        <v>474901</v>
       </c>
       <c r="R3" t="n">
-        <v>6991352</v>
+        <v>6991331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en ung björk.</t>
+          <t>Flera fruktkroppar i stambasen av en grov gran med 53 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +896,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751190</v>
+        <v>129751192</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,26 +945,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474901</v>
+        <v>474859</v>
       </c>
       <c r="R4" t="n">
-        <v>6991331</v>
+        <v>6991352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en grov gran med 53 cm i brösthöjdsdiameter.</t>
+          <t>På en ung björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1327,42 +1327,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751172</v>
+        <v>129751167</v>
       </c>
       <c r="B7" t="n">
-        <v>99108</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474858</v>
+        <v>474740</v>
       </c>
       <c r="R7" t="n">
-        <v>6991515</v>
+        <v>6991364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,19 +1412,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en döende gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751202</v>
+        <v>129751172</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>99108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,42 +1477,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474679</v>
+        <v>474858</v>
       </c>
       <c r="R8" t="n">
-        <v>6991397</v>
+        <v>6991515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1553,42 +1581,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751167</v>
+        <v>129751181</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1600,10 +1636,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474740</v>
+        <v>474845</v>
       </c>
       <c r="R9" t="n">
-        <v>6991364</v>
+        <v>6991430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1640,7 +1676,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en döende gran.</t>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,32 +1685,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1692,65 +1709,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751181</v>
+        <v>129751202</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474845</v>
+        <v>474679</v>
       </c>
       <c r="R10" t="n">
-        <v>6991430</v>
+        <v>6991397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1785,11 +1790,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -3017,42 +3017,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751168</v>
+        <v>129751173</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>99108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474663</v>
+        <v>474703</v>
       </c>
       <c r="R20" t="n">
-        <v>6991235</v>
+        <v>6991289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3102,43 +3102,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3156,42 +3132,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751173</v>
+        <v>129751168</v>
       </c>
       <c r="B21" t="n">
-        <v>99108</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3203,10 +3179,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474703</v>
+        <v>474663</v>
       </c>
       <c r="R21" t="n">
-        <v>6991289</v>
+        <v>6991235</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3241,19 +3217,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3662,48 +3662,65 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751171</v>
+        <v>129751187</v>
       </c>
       <c r="B25" t="n">
-        <v>80214</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474852</v>
+        <v>474778</v>
       </c>
       <c r="R25" t="n">
-        <v>6991438</v>
+        <v>6991301</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3740,7 +3757,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3755,7 +3772,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3773,65 +3790,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751187</v>
+        <v>129751171</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474778</v>
+        <v>474852</v>
       </c>
       <c r="R26" t="n">
-        <v>6991301</v>
+        <v>6991438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>På sidan av ett stort block i tallskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751186</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129751190</v>
       </c>
       <c r="B3" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1327,42 +1327,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751167</v>
+        <v>129751172</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>99112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474740</v>
+        <v>474858</v>
       </c>
       <c r="R7" t="n">
-        <v>6991364</v>
+        <v>6991515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,43 +1412,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en döende gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,42 +1442,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751172</v>
+        <v>129751167</v>
       </c>
       <c r="B8" t="n">
-        <v>99108</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1513,10 +1489,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474858</v>
+        <v>474740</v>
       </c>
       <c r="R8" t="n">
-        <v>6991515</v>
+        <v>6991364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,19 +1527,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en döende gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
         <v>129751181</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>129751202</v>
       </c>
       <c r="B10" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129751182</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>129751206</v>
       </c>
       <c r="B14" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751191</v>
+        <v>129751170</v>
       </c>
       <c r="B16" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,24 +2492,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474691</v>
+        <v>474880</v>
       </c>
       <c r="R16" t="n">
-        <v>6991403</v>
+        <v>6991500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2568,13 +2573,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2612,10 +2616,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751170</v>
+        <v>129751191</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>91617</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2623,29 +2627,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2655,10 +2654,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474880</v>
+        <v>474691</v>
       </c>
       <c r="R17" t="n">
-        <v>6991500</v>
+        <v>6991403</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2695,7 +2694,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2704,12 +2703,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3017,42 +3017,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751173</v>
+        <v>129751168</v>
       </c>
       <c r="B20" t="n">
-        <v>99108</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474703</v>
+        <v>474663</v>
       </c>
       <c r="R20" t="n">
-        <v>6991289</v>
+        <v>6991235</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3102,19 +3102,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3132,42 +3156,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751168</v>
+        <v>129751173</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>99112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3179,10 +3203,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474663</v>
+        <v>474703</v>
       </c>
       <c r="R21" t="n">
-        <v>6991235</v>
+        <v>6991289</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3217,43 +3241,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>129751185</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129751188</v>
       </c>
       <c r="B23" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129751183</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,65 +3662,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751187</v>
+        <v>129751171</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474778</v>
+        <v>474852</v>
       </c>
       <c r="R25" t="n">
-        <v>6991301</v>
+        <v>6991438</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3757,7 +3740,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>På sidan av ett stort block i tallskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3772,7 +3755,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3790,48 +3773,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751171</v>
+        <v>129751187</v>
       </c>
       <c r="B26" t="n">
-        <v>80214</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474852</v>
+        <v>474778</v>
       </c>
       <c r="R26" t="n">
-        <v>6991438</v>
+        <v>6991301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
         <v>129751203</v>
       </c>
       <c r="B27" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129751180</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4140,42 +4140,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751189</v>
+        <v>129751197</v>
       </c>
       <c r="B29" t="n">
-        <v>98673</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4183,10 +4178,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474683</v>
+        <v>474867</v>
       </c>
       <c r="R29" t="n">
-        <v>6991447</v>
+        <v>6991490</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4238,7 +4233,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4256,65 +4271,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751184</v>
+        <v>129751189</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>98677</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474889</v>
+        <v>474683</v>
       </c>
       <c r="R30" t="n">
-        <v>6991473</v>
+        <v>6991447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4351,7 +4354,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4366,7 +4369,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4384,48 +4387,65 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751197</v>
+        <v>129751184</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474867</v>
+        <v>474889</v>
       </c>
       <c r="R31" t="n">
-        <v>6991490</v>
+        <v>6991473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4478,26 +4498,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4518,7 +4518,7 @@
         <v>129751205</v>
       </c>
       <c r="B32" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129751196</v>
+        <v>129751169</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4637,37 +4637,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474884</v>
+        <v>474788</v>
       </c>
       <c r="R33" t="n">
-        <v>6991431</v>
+        <v>6991283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4704,7 +4713,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4713,13 +4722,12 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4734,12 +4742,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4757,10 +4765,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129751169</v>
+        <v>129751196</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4768,46 +4776,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474788</v>
+        <v>474884</v>
       </c>
       <c r="R34" t="n">
-        <v>6991283</v>
+        <v>6991431</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4844,7 +4843,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4853,12 +4852,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751186</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129751190</v>
       </c>
       <c r="B3" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1327,39 +1327,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751172</v>
+        <v>129751181</v>
       </c>
       <c r="B7" t="n">
-        <v>99112</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1374,10 +1382,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474858</v>
+        <v>474845</v>
       </c>
       <c r="R7" t="n">
-        <v>6991515</v>
+        <v>6991430</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,6 +1420,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1424,7 +1437,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1581,47 +1594,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751181</v>
+        <v>129751172</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>99114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1636,10 +1641,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474845</v>
+        <v>474858</v>
       </c>
       <c r="R9" t="n">
-        <v>6991430</v>
+        <v>6991515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,11 +1679,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
         <v>129751202</v>
       </c>
       <c r="B10" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129751182</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>129751206</v>
       </c>
       <c r="B14" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751170</v>
+        <v>129751191</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>91619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,29 +2492,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474880</v>
+        <v>474691</v>
       </c>
       <c r="R16" t="n">
-        <v>6991500</v>
+        <v>6991403</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2573,12 +2568,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2616,10 +2612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751191</v>
+        <v>129751170</v>
       </c>
       <c r="B17" t="n">
-        <v>91617</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2627,24 +2623,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2654,10 +2655,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474691</v>
+        <v>474880</v>
       </c>
       <c r="R17" t="n">
-        <v>6991403</v>
+        <v>6991500</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2694,7 +2695,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2703,13 +2704,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3017,42 +3017,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751168</v>
+        <v>129751173</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>99114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474663</v>
+        <v>474703</v>
       </c>
       <c r="R20" t="n">
-        <v>6991235</v>
+        <v>6991289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3102,43 +3102,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3156,42 +3132,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751173</v>
+        <v>129751168</v>
       </c>
       <c r="B21" t="n">
-        <v>99112</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3203,10 +3179,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474703</v>
+        <v>474663</v>
       </c>
       <c r="R21" t="n">
-        <v>6991289</v>
+        <v>6991235</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3241,19 +3217,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>129751185</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129751188</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129751183</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,48 +3662,65 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751171</v>
+        <v>129751187</v>
       </c>
       <c r="B25" t="n">
-        <v>80214</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474852</v>
+        <v>474778</v>
       </c>
       <c r="R25" t="n">
-        <v>6991438</v>
+        <v>6991301</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3740,7 +3757,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3755,7 +3772,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3773,65 +3790,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751187</v>
+        <v>129751171</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>80214</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474778</v>
+        <v>474852</v>
       </c>
       <c r="R26" t="n">
-        <v>6991301</v>
+        <v>6991438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>På sidan av ett stort block i tallskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
         <v>129751203</v>
       </c>
       <c r="B27" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129751180</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4271,53 +4271,65 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B30" t="n">
-        <v>98677</v>
+        <v>98780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R30" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4354,7 +4366,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4369,7 +4381,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4387,65 +4399,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751184</v>
+        <v>129751189</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>98679</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474889</v>
+        <v>474683</v>
       </c>
       <c r="R31" t="n">
-        <v>6991473</v>
+        <v>6991447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4518,7 +4518,7 @@
         <v>129751205</v>
       </c>
       <c r="B32" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -4271,65 +4271,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751184</v>
+        <v>129751189</v>
       </c>
       <c r="B30" t="n">
-        <v>98780</v>
+        <v>98679</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474889</v>
+        <v>474683</v>
       </c>
       <c r="R30" t="n">
-        <v>6991473</v>
+        <v>6991447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4366,7 +4354,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4381,7 +4369,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4399,53 +4387,65 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B31" t="n">
-        <v>98679</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R31" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129751169</v>
+        <v>129751196</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4637,46 +4637,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474788</v>
+        <v>474884</v>
       </c>
       <c r="R33" t="n">
-        <v>6991283</v>
+        <v>6991431</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4713,7 +4704,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4722,12 +4713,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4742,12 +4734,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4765,10 +4757,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129751196</v>
+        <v>129751169</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4776,37 +4768,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474884</v>
+        <v>474788</v>
       </c>
       <c r="R34" t="n">
-        <v>6991431</v>
+        <v>6991283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4843,7 +4844,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4852,13 +4853,12 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -1327,50 +1327,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751181</v>
+        <v>129751167</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1382,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474845</v>
+        <v>474740</v>
       </c>
       <c r="R7" t="n">
-        <v>6991430</v>
+        <v>6991364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,7 +1414,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+          <t>Ringhack, äldre, på en döende gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,13 +1423,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1455,42 +1466,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751167</v>
+        <v>129751172</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>99114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1502,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474740</v>
+        <v>474858</v>
       </c>
       <c r="R8" t="n">
-        <v>6991364</v>
+        <v>6991515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,43 +1551,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en döende gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1594,10 +1581,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751172</v>
+        <v>129751202</v>
       </c>
       <c r="B9" t="n">
-        <v>99114</v>
+        <v>100969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,46 +1592,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474858</v>
+        <v>474679</v>
       </c>
       <c r="R9" t="n">
-        <v>6991515</v>
+        <v>6991397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1709,53 +1692,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751202</v>
+        <v>129751181</v>
       </c>
       <c r="B10" t="n">
-        <v>100969</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474679</v>
+        <v>474845</v>
       </c>
       <c r="R10" t="n">
-        <v>6991397</v>
+        <v>6991430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1790,6 +1785,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -3662,65 +3662,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751187</v>
+        <v>129751171</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>80214</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474778</v>
+        <v>474852</v>
       </c>
       <c r="R25" t="n">
-        <v>6991301</v>
+        <v>6991438</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3757,7 +3740,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>På sidan av ett stort block i tallskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3772,7 +3755,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3790,48 +3773,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751171</v>
+        <v>129751187</v>
       </c>
       <c r="B26" t="n">
-        <v>80214</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474852</v>
+        <v>474778</v>
       </c>
       <c r="R26" t="n">
-        <v>6991438</v>
+        <v>6991301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -3662,48 +3662,65 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751171</v>
+        <v>129751187</v>
       </c>
       <c r="B25" t="n">
-        <v>80214</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474852</v>
+        <v>474778</v>
       </c>
       <c r="R25" t="n">
-        <v>6991438</v>
+        <v>6991301</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3740,7 +3757,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3755,7 +3772,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3773,65 +3790,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751187</v>
+        <v>129751171</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>80214</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474778</v>
+        <v>474852</v>
       </c>
       <c r="R26" t="n">
-        <v>6991301</v>
+        <v>6991438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>På sidan av ett stort block i tallskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751186</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129751172</v>
       </c>
       <c r="B8" t="n">
-        <v>99114</v>
+        <v>99124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,53 +1581,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751202</v>
+        <v>129751181</v>
       </c>
       <c r="B9" t="n">
-        <v>100969</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474679</v>
+        <v>474845</v>
       </c>
       <c r="R9" t="n">
-        <v>6991397</v>
+        <v>6991430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1662,6 +1674,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1674,7 +1691,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1692,65 +1709,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751181</v>
+        <v>129751202</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>100979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474845</v>
+        <v>474679</v>
       </c>
       <c r="R10" t="n">
-        <v>6991430</v>
+        <v>6991397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1785,11 +1790,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2101,7 +2101,7 @@
         <v>129751182</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>129751206</v>
       </c>
       <c r="B14" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>129751173</v>
       </c>
       <c r="B20" t="n">
-        <v>99114</v>
+        <v>99124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129751185</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129751183</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,65 +3662,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751187</v>
+        <v>129751171</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>80214</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474778</v>
+        <v>474852</v>
       </c>
       <c r="R25" t="n">
-        <v>6991301</v>
+        <v>6991438</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3757,7 +3740,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>På sidan av ett stort block i tallskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3772,7 +3755,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3790,48 +3773,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751171</v>
+        <v>129751187</v>
       </c>
       <c r="B26" t="n">
-        <v>80214</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474852</v>
+        <v>474778</v>
       </c>
       <c r="R26" t="n">
-        <v>6991438</v>
+        <v>6991301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
         <v>129751203</v>
       </c>
       <c r="B27" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129751180</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129751189</v>
       </c>
       <c r="B30" t="n">
-        <v>98679</v>
+        <v>98689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>129751184</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>129751205</v>
       </c>
       <c r="B32" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -4271,53 +4271,65 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B30" t="n">
-        <v>98689</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R30" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4354,7 +4366,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4369,7 +4381,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4387,65 +4399,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751184</v>
+        <v>129751189</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>98689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474889</v>
+        <v>474683</v>
       </c>
       <c r="R31" t="n">
-        <v>6991473</v>
+        <v>6991447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751186</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129751190</v>
       </c>
       <c r="B3" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>129751192</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>129751194</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>129751193</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>129751167</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,39 +1466,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751172</v>
+        <v>129751181</v>
       </c>
       <c r="B8" t="n">
-        <v>99124</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1513,10 +1521,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474858</v>
+        <v>474845</v>
       </c>
       <c r="R8" t="n">
-        <v>6991515</v>
+        <v>6991430</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,6 +1559,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1563,7 +1576,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,65 +1594,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751181</v>
+        <v>129751202</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>100983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474845</v>
+        <v>474679</v>
       </c>
       <c r="R9" t="n">
-        <v>6991430</v>
+        <v>6991397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,11 +1675,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1687,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,10 +1705,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751202</v>
+        <v>129751172</v>
       </c>
       <c r="B10" t="n">
-        <v>100979</v>
+        <v>99128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,42 +1716,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474679</v>
+        <v>474858</v>
       </c>
       <c r="R10" t="n">
-        <v>6991397</v>
+        <v>6991515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
         <v>129751165</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129751166</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>129751182</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>129751206</v>
       </c>
       <c r="B14" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129751163</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129751191</v>
       </c>
       <c r="B16" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>129751170</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>129751195</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>129751164</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3017,42 +3017,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751173</v>
+        <v>129751168</v>
       </c>
       <c r="B20" t="n">
-        <v>99124</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474703</v>
+        <v>474663</v>
       </c>
       <c r="R20" t="n">
-        <v>6991289</v>
+        <v>6991235</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3102,19 +3102,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3132,42 +3156,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751168</v>
+        <v>129751173</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>99128</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3179,10 +3203,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474663</v>
+        <v>474703</v>
       </c>
       <c r="R21" t="n">
-        <v>6991235</v>
+        <v>6991289</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3217,43 +3241,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
         <v>129751185</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129751188</v>
       </c>
       <c r="B23" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129751183</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>129751171</v>
       </c>
       <c r="B25" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>129751187</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>129751203</v>
       </c>
       <c r="B27" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129751180</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>129751197</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4271,65 +4271,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751184</v>
+        <v>129751189</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>98693</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474889</v>
+        <v>474683</v>
       </c>
       <c r="R30" t="n">
-        <v>6991473</v>
+        <v>6991447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4366,7 +4354,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4381,7 +4369,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4399,53 +4387,65 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751189</v>
+        <v>129751184</v>
       </c>
       <c r="B31" t="n">
-        <v>98689</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474683</v>
+        <v>474889</v>
       </c>
       <c r="R31" t="n">
-        <v>6991447</v>
+        <v>6991473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4518,7 +4518,7 @@
         <v>129751205</v>
       </c>
       <c r="B32" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>129751196</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>129751169</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -1466,47 +1466,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751181</v>
+        <v>129751172</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>99128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1521,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474845</v>
+        <v>474858</v>
       </c>
       <c r="R8" t="n">
-        <v>6991430</v>
+        <v>6991515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,11 +1551,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1576,7 +1563,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1594,53 +1581,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751202</v>
+        <v>129751181</v>
       </c>
       <c r="B9" t="n">
-        <v>100983</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474679</v>
+        <v>474845</v>
       </c>
       <c r="R9" t="n">
-        <v>6991397</v>
+        <v>6991430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,6 +1674,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1687,7 +1691,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1705,10 +1709,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751172</v>
+        <v>129751202</v>
       </c>
       <c r="B10" t="n">
-        <v>99128</v>
+        <v>100983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,46 +1720,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474858</v>
+        <v>474679</v>
       </c>
       <c r="R10" t="n">
-        <v>6991515</v>
+        <v>6991397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751191</v>
+        <v>129751170</v>
       </c>
       <c r="B16" t="n">
-        <v>91622</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,24 +2492,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474691</v>
+        <v>474880</v>
       </c>
       <c r="R16" t="n">
-        <v>6991403</v>
+        <v>6991500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2568,13 +2573,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2612,10 +2616,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751170</v>
+        <v>129751191</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>91622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2623,29 +2627,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2655,10 +2654,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474880</v>
+        <v>474691</v>
       </c>
       <c r="R17" t="n">
-        <v>6991500</v>
+        <v>6991403</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2695,7 +2694,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2704,12 +2703,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2747,10 +2747,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751195</v>
+        <v>129751164</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,37 +2758,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474864</v>
+        <v>474821</v>
       </c>
       <c r="R18" t="n">
-        <v>6991382</v>
+        <v>6991298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,7 +2834,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran i barrblandskog.</t>
+          <t>Ringhack, färska, på en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2834,13 +2843,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2855,12 +2863,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2878,10 +2886,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751164</v>
+        <v>129751195</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,46 +2897,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474821</v>
+        <v>474864</v>
       </c>
       <c r="R19" t="n">
-        <v>6991298</v>
+        <v>6991382</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2965,7 +2964,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en hyfsat grov gran.</t>
+          <t>Enstaka bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2974,12 +2973,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129751196</v>
+        <v>129751169</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4637,37 +4637,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474884</v>
+        <v>474788</v>
       </c>
       <c r="R33" t="n">
-        <v>6991431</v>
+        <v>6991283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4704,7 +4713,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4713,13 +4722,12 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4734,12 +4742,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4757,10 +4765,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129751169</v>
+        <v>129751196</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4768,46 +4776,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474788</v>
+        <v>474884</v>
       </c>
       <c r="R34" t="n">
-        <v>6991283</v>
+        <v>6991431</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4844,7 +4843,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4853,12 +4852,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -1327,57 +1327,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751167</v>
+        <v>129751202</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>100983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474740</v>
+        <v>474679</v>
       </c>
       <c r="R7" t="n">
-        <v>6991364</v>
+        <v>6991397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1412,43 +1408,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en döende gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,42 +1438,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751172</v>
+        <v>129751167</v>
       </c>
       <c r="B8" t="n">
-        <v>99128</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1513,10 +1485,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474858</v>
+        <v>474740</v>
       </c>
       <c r="R8" t="n">
-        <v>6991515</v>
+        <v>6991364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,19 +1523,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en döende gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,47 +1577,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751181</v>
+        <v>129751172</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>99128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1636,10 +1624,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474845</v>
+        <v>474858</v>
       </c>
       <c r="R9" t="n">
-        <v>6991430</v>
+        <v>6991515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,11 +1662,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1691,7 +1674,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1709,53 +1692,65 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751202</v>
+        <v>129751181</v>
       </c>
       <c r="B10" t="n">
-        <v>100983</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474679</v>
+        <v>474845</v>
       </c>
       <c r="R10" t="n">
-        <v>6991397</v>
+        <v>6991430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1790,6 +1785,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129751186</v>
+        <v>129751188</v>
       </c>
       <c r="B2" t="n">
-        <v>98830</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474867</v>
+        <v>474794</v>
       </c>
       <c r="R2" t="n">
-        <v>6991494</v>
+        <v>6991300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 2 vinterståndare inom ca 1 m2 yta på en mossklädd upphöjning.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +773,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,37 +810,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751190</v>
+        <v>129751192</v>
       </c>
       <c r="B3" t="n">
-        <v>91658</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474901</v>
+        <v>474859</v>
       </c>
       <c r="R3" t="n">
-        <v>6991331</v>
+        <v>6991352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en grov gran med 53 cm i brösthöjdsdiameter.</t>
+          <t>På en ung björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +903,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,14 +941,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751192</v>
+        <v>129751193</v>
       </c>
       <c r="B4" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -972,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474859</v>
+        <v>474875</v>
       </c>
       <c r="R4" t="n">
-        <v>6991352</v>
+        <v>6991364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en ung björk.</t>
+          <t>På en gran intill andra hänglavar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,12 +1039,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1047,7 +1054,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,11 +1075,11 @@
         <v>129751194</v>
       </c>
       <c r="B5" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1196,14 +1203,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751193</v>
+        <v>129751195</v>
       </c>
       <c r="B6" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1234,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474875</v>
+        <v>474864</v>
       </c>
       <c r="R6" t="n">
-        <v>6991364</v>
+        <v>6991382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1281,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en gran intill andra hänglavar.</t>
+          <t>Enstaka bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,57 +1334,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751167</v>
+        <v>129751196</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474740</v>
+        <v>474884</v>
       </c>
       <c r="R7" t="n">
-        <v>6991364</v>
+        <v>6991431</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1412,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en döende gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,6 +1421,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1443,12 +1442,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751181</v>
+        <v>129751197</v>
       </c>
       <c r="B8" t="n">
-        <v>98830</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,54 +1476,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474845</v>
+        <v>474867</v>
       </c>
       <c r="R8" t="n">
-        <v>6991430</v>
+        <v>6991490</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1561,7 +1543,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,7 +1558,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1594,10 +1596,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751202</v>
+        <v>129751171</v>
       </c>
       <c r="B9" t="n">
-        <v>101019</v>
+        <v>80460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,31 +1607,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1637,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474679</v>
+        <v>474852</v>
       </c>
       <c r="R9" t="n">
-        <v>6991397</v>
+        <v>6991438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,6 +1672,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sidan av ett stort block i tallskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1687,7 +1689,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1705,10 +1707,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751172</v>
+        <v>129751170</v>
       </c>
       <c r="B10" t="n">
-        <v>99164</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,46 +1718,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474858</v>
+        <v>474880</v>
       </c>
       <c r="R10" t="n">
-        <v>6991515</v>
+        <v>6991500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1790,19 +1788,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1820,10 +1842,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751165</v>
+        <v>129751163</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,10 +1889,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474824</v>
+        <v>474969</v>
       </c>
       <c r="R11" t="n">
-        <v>6991300</v>
+        <v>6991400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,7 +1929,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, som bedöms 5-10 år gamla, i riklig mängd på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1959,10 +1981,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751166</v>
+        <v>129751164</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2006,10 +2028,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474782</v>
+        <v>474821</v>
       </c>
       <c r="R12" t="n">
-        <v>6991306</v>
+        <v>6991298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2046,7 +2068,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran. På fyndplatsen finns stående död ved i en sådan volym som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska, på en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,50 +2120,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751182</v>
+        <v>129751165</v>
       </c>
       <c r="B13" t="n">
-        <v>98830</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2153,10 +2167,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474843</v>
+        <v>474824</v>
       </c>
       <c r="R13" t="n">
-        <v>6991394</v>
+        <v>6991300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2193,7 +2207,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta i tallskog.</t>
+          <t>Ringhack, äldre, som bedöms 5-10 år gamla, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,18 +2216,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Med inslag av gran och björk.</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2231,53 +2259,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751206</v>
+        <v>129751166</v>
       </c>
       <c r="B14" t="n">
-        <v>101019</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474663</v>
+        <v>474782</v>
       </c>
       <c r="R14" t="n">
-        <v>6991239</v>
+        <v>6991306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2312,19 +2344,43 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran. På fyndplatsen finns stående död ved i en sådan volym som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2342,10 +2398,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751163</v>
+        <v>129751167</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,10 +2445,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474969</v>
+        <v>474740</v>
       </c>
       <c r="R15" t="n">
-        <v>6991400</v>
+        <v>6991364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2429,7 +2485,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på en döende gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2443,7 +2499,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2481,10 +2537,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751191</v>
+        <v>129751168</v>
       </c>
       <c r="B16" t="n">
-        <v>91658</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2492,37 +2548,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474691</v>
+        <v>474663</v>
       </c>
       <c r="R16" t="n">
-        <v>6991403</v>
+        <v>6991235</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2559,7 +2624,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2568,13 +2633,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2589,12 +2653,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2612,10 +2676,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751170</v>
+        <v>129751169</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2623,16 +2687,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2648,17 +2712,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474880</v>
+        <v>474788</v>
       </c>
       <c r="R17" t="n">
-        <v>6991500</v>
+        <v>6991283</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2695,7 +2763,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med full längd.</t>
+          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2724,12 +2792,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2747,37 +2815,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751195</v>
+        <v>129751189</v>
       </c>
       <c r="B18" t="n">
-        <v>79094</v>
+        <v>99017</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219795</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2785,10 +2858,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474864</v>
+        <v>474683</v>
       </c>
       <c r="R18" t="n">
-        <v>6991382</v>
+        <v>6991447</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,14 +2898,14 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran i barrblandskog.</t>
+          <t>En vinterståndare mest troligt av grönkulla.</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
@@ -2841,26 +2914,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2878,42 +2931,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751164</v>
+        <v>129751172</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>99456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2925,10 +2978,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474821</v>
+        <v>474858</v>
       </c>
       <c r="R19" t="n">
-        <v>6991298</v>
+        <v>6991515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2963,43 +3016,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en hyfsat grov gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3017,42 +3046,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751168</v>
+        <v>129751173</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>99456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3064,10 +3093,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474663</v>
+        <v>474703</v>
       </c>
       <c r="R20" t="n">
-        <v>6991235</v>
+        <v>6991289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3102,43 +3131,19 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd längs minst 6 meter på en rätt grov gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3156,39 +3161,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751173</v>
+        <v>129751180</v>
       </c>
       <c r="B21" t="n">
-        <v>99164</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>bladfällning, vissnar</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3203,10 +3216,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474703</v>
+        <v>474708</v>
       </c>
       <c r="R21" t="n">
-        <v>6991289</v>
+        <v>6991357</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3239,6 +3252,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3271,10 +3289,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751185</v>
+        <v>129751181</v>
       </c>
       <c r="B22" t="n">
-        <v>98830</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3301,17 +3319,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3326,10 +3344,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474834</v>
+        <v>474845</v>
       </c>
       <c r="R22" t="n">
-        <v>6991493</v>
+        <v>6991430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3366,7 +3384,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare ca 4 meter norr om ett stort mossöverväxt stenblock.</t>
+          <t>Minst 50  plantor och 3 vinterståndare inom ca 2 m2 yta ca 5 meter väster om ett stort överväxt block i tallskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3381,7 +3399,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3399,52 +3417,65 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751188</v>
+        <v>129751182</v>
       </c>
       <c r="B23" t="n">
-        <v>91634</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474794</v>
+        <v>474843</v>
       </c>
       <c r="R23" t="n">
-        <v>6991300</v>
+        <v>6991394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3481,7 +3512,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en stående hackspettsbearbetad död gran med full längd.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta i tallskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3496,27 +3527,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Med inslag av gran och björk.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3537,7 +3553,7 @@
         <v>129751183</v>
       </c>
       <c r="B24" t="n">
-        <v>98830</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,48 +3678,65 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751171</v>
+        <v>129751184</v>
       </c>
       <c r="B25" t="n">
-        <v>80227</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474852</v>
+        <v>474889</v>
       </c>
       <c r="R25" t="n">
-        <v>6991438</v>
+        <v>6991473</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3740,7 +3773,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På sidan av ett stort block i tallskog.</t>
+          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3755,7 +3788,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3773,10 +3806,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751187</v>
+        <v>129751185</v>
       </c>
       <c r="B26" t="n">
-        <v>98830</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3803,17 +3836,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3828,10 +3861,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474778</v>
+        <v>474834</v>
       </c>
       <c r="R26" t="n">
-        <v>6991301</v>
+        <v>6991493</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3868,7 +3901,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
+          <t>Minst 1 vinterståndare ca 4 meter norr om ett stort mossöverväxt stenblock.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3883,7 +3916,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3901,53 +3934,65 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751203</v>
+        <v>129751186</v>
       </c>
       <c r="B27" t="n">
-        <v>101019</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474702</v>
+        <v>474867</v>
       </c>
       <c r="R27" t="n">
-        <v>6991285</v>
+        <v>6991494</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3982,6 +4027,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 2 vinterståndare inom ca 1 m2 yta på en mossklädd upphöjning.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3994,7 +4044,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4012,10 +4062,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751180</v>
+        <v>129751187</v>
       </c>
       <c r="B28" t="n">
-        <v>98830</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4042,7 +4092,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4067,10 +4117,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474708</v>
+        <v>474778</v>
       </c>
       <c r="R28" t="n">
-        <v>6991357</v>
+        <v>6991301</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4107,7 +4157,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 3 plantor och 1 vinterståndare inom ca 0,5 m2 yta.</t>
+          <t>Minst 16 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en gran med ringhack av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4122,7 +4172,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4140,65 +4190,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751184</v>
+        <v>129751202</v>
       </c>
       <c r="B29" t="n">
-        <v>98830</v>
+        <v>101325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kojmon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474889</v>
+        <v>474679</v>
       </c>
       <c r="R29" t="n">
-        <v>6991473</v>
+        <v>6991397</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4233,11 +4271,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 87 plantor och 2 vinterståndare inom ca 0,5 m2 yta på ett upphöjt mosstäckt markparti.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4250,7 +4283,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4268,37 +4301,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751197</v>
+        <v>129751203</v>
       </c>
       <c r="B30" t="n">
-        <v>79094</v>
+        <v>101325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4306,10 +4344,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474867</v>
+        <v>474702</v>
       </c>
       <c r="R30" t="n">
-        <v>6991490</v>
+        <v>6991285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4344,11 +4382,6 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4361,27 +4394,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4399,10 +4412,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751189</v>
+        <v>129751205</v>
       </c>
       <c r="B31" t="n">
-        <v>98729</v>
+        <v>101325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4410,28 +4423,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4442,10 +4455,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474683</v>
+        <v>474671</v>
       </c>
       <c r="R31" t="n">
-        <v>6991447</v>
+        <v>6991282</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4480,16 +4493,11 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En vinterståndare mest troligt av grönkulla.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
@@ -4515,10 +4523,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751205</v>
+        <v>129751206</v>
       </c>
       <c r="B32" t="n">
-        <v>101019</v>
+        <v>101325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4558,10 +4566,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474671</v>
+        <v>474663</v>
       </c>
       <c r="R32" t="n">
-        <v>6991282</v>
+        <v>6991239</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4608,7 +4616,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4623,276 +4631,6 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>129751196</v>
-      </c>
-      <c r="B33" t="n">
-        <v>79094</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Kojmon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>474884</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6991431</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>129751169</v>
-      </c>
-      <c r="B34" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Kojmon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>474788</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6991283</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en rätt grov gran.</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49056-2025 artfynd.xlsx
+++ b/artfynd/A 49056-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751192</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1069,6 +1084,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1200,6 +1220,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751194</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1331,6 +1356,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751195</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1462,6 +1492,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751196</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1593,6 +1628,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751197</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1704,6 +1744,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751171</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1839,6 +1884,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751170</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1978,6 +2028,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751163</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2117,6 +2172,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751164</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2256,6 +2316,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751165</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2395,6 +2460,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751166</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2534,6 +2604,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751167</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2673,6 +2748,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751168</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2812,6 +2892,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751169</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2928,6 +3013,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751189</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3043,6 +3133,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751172</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3158,6 +3253,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751173</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3286,6 +3386,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751180</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3414,6 +3519,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751181</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3547,6 +3657,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751182</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3675,6 +3790,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751183</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3803,6 +3923,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751184</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3931,6 +4056,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751185</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4059,6 +4189,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751186</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4187,6 +4322,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751187</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4298,6 +4438,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751202</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4409,6 +4554,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751203</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4520,6 +4670,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751205</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4631,8 +4786,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751206</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>